--- a/BEARX-GUI-Examples/PlainTimeInvariant/tables/ConditioningPlan.xlsx
+++ b/BEARX-GUI-Examples/PlainTimeInvariant/tables/ConditioningPlan.xlsx
@@ -590,9 +590,6 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
